--- a/tiflow-rx/build/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Communication-DispReq.xlsx
+++ b/tiflow-rx/build/1.0.0-draft/StructureDefinition-GEM-ERP-PR-Communication-DispReq.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1787" uniqueCount="357">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1778" uniqueCount="348">
   <si>
     <t>Property</t>
   </si>
@@ -468,6 +468,10 @@
     <t>Definiert den Typ des Rezepts. Das Codesystem enthält alle unterstützten Formulare.</t>
   </si>
   <si>
+    <t xml:space="preserve">ele-1
+</t>
+  </si>
+  <si>
     <t>Communication.modifierExtension</t>
   </si>
   <si>
@@ -510,17 +514,10 @@
     <t>Allows identification of the communication as it is known by various participating systems and in a way that remains consistent across servers.</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1
-</t>
-  </si>
-  <si>
     <t>Event.identifier</t>
   </si>
   <si>
     <t>FiveWs.identifier</t>
-  </si>
-  <si>
-    <t>II - The Identifier class is a little looser than the v3 type II because it allows URIs as well as registered OIDs or GUIDs.  Also maps to Role[classCode=IDENT]</t>
   </si>
   <si>
     <t>Communication.instantiatesCanonical</t>
@@ -536,9 +533,6 @@
     <t>The URL pointing to a FHIR-defined protocol, guideline, orderset or other definition that is adhered to in whole or in part by this Communication.</t>
   </si>
   <si>
-    <t>see [Canonical References](http://hl7.org/fhir/R4/references.html#canonical)</t>
-  </si>
-  <si>
     <t>Event.instantiatesCanonical</t>
   </si>
   <si>
@@ -580,14 +574,7 @@
     <t>This must point to some sort of a 'Request' resource, such as CarePlan, CommunicationRequest, ServiceRequest, MedicationRequest, etc.</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ref-1:SHALL have a contained resource if a local reference is provided {reference.startsWith('#').not() or (reference.substring(1).trace('url') in %rootResource.contained.id.trace('ids'))}</t>
-  </si>
-  <si>
     <t>Event.basedOn</t>
-  </si>
-  <si>
-    <t>The target of a resource reference is a RIM entry point (Act, Role, or Entity)</t>
   </si>
   <si>
     <t>Communication.partOf</t>
@@ -603,9 +590,6 @@
     <t>Part of this action.</t>
   </si>
   <si>
-    <t>References SHALL be a reference to an actual FHIR resource, and SHALL be resolveable (allowing for access control, temporary unavailability, etc.). Resolution can be either by retrieval from the URL, or, where applicable by resource type, by treating an absolute reference as a canonical URL and looking it up in a local registry/repository.</t>
-  </si>
-  <si>
     <t>Event.partOf</t>
   </si>
   <si>
@@ -681,9 +665,6 @@
     <t>Event.statusReason</t>
   </si>
   <si>
-    <t>CD</t>
-  </si>
-  <si>
     <t>Communication.category</t>
   </si>
   <si>
@@ -736,9 +717,6 @@
   </si>
   <si>
     <t>A channel that was used for this communication (e.g. email, fax).</t>
-  </si>
-  <si>
-    <t>Not all terminology uses fit this general pattern. In some cases, models should not use CodeableConcept and use Coding directly and provide their own structure for managing text, codings, translations and the relationship between elements and pre- and post-coordination.</t>
   </si>
   <si>
     <t>Codes for communication mediums such as phone, fax, email, in person, etc.</t>
@@ -1126,13 +1104,7 @@
     <t>Additional notes or commentary about the communication by the sender, receiver or other interested parties.</t>
   </si>
   <si>
-    <t>For systems that do not have structured annotations, they can simply communicate a single annotation with no author or time.  This element may need to be included in narrative because of the potential for modifying information.  *Annotations SHOULD NOT* be used to communicate "modifying" information that could be computable. (This is a SHOULD because enforcing user behavior is nearly impossible).</t>
-  </si>
-  <si>
     <t>Event.note</t>
-  </si>
-  <si>
-    <t>Act</t>
   </si>
 </sst>
 </file>
@@ -1493,7 +1465,7 @@
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="43.421875" customWidth="true" bestFit="true"/>
     <col min="38" max="38" width="31.65234375" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="123.23828125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="38.5234375" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2593,7 +2565,7 @@
         <v>79</v>
       </c>
       <c r="AI10" t="s" s="2">
-        <v>77</v>
+        <v>145</v>
       </c>
       <c r="AJ10" t="s" s="2">
         <v>139</v>
@@ -2610,14 +2582,14 @@
     </row>
     <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="C11" s="2"/>
       <c r="D11" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E11" s="2"/>
       <c r="F11" t="s" s="2">
@@ -2639,16 +2611,16 @@
         <v>132</v>
       </c>
       <c r="L11" t="s" s="2">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="M11" t="s" s="2">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="N11" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O11" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P11" t="s" s="2">
         <v>77</v>
@@ -2685,19 +2657,19 @@
         <v>77</v>
       </c>
       <c r="AB11" t="s" s="2">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="AC11" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AD11" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE11" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AF11" t="s" s="2">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="AG11" t="s" s="2">
         <v>78</v>
@@ -2723,10 +2695,10 @@
     </row>
     <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C12" s="2"/>
       <c r="D12" t="s" s="2">
@@ -2749,19 +2721,19 @@
         <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="N12" t="s" s="2">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O12" t="s" s="2">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="P12" t="s" s="2">
         <v>77</v>
@@ -2810,7 +2782,7 @@
         <v>77</v>
       </c>
       <c r="AF12" t="s" s="2">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="AG12" t="s" s="2">
         <v>78</v>
@@ -2819,7 +2791,7 @@
         <v>79</v>
       </c>
       <c r="AI12" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AJ12" t="s" s="2">
         <v>99</v>
@@ -2831,15 +2803,15 @@
         <v>160</v>
       </c>
       <c r="AM12" t="s" s="2">
-        <v>161</v>
+        <v>77</v>
       </c>
     </row>
     <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="B13" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
@@ -2862,17 +2834,15 @@
         <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
+        <v>162</v>
+      </c>
+      <c r="L13" t="s" s="2">
         <v>163</v>
       </c>
-      <c r="L13" t="s" s="2">
+      <c r="M13" t="s" s="2">
         <v>164</v>
       </c>
-      <c r="M13" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N13" t="s" s="2">
-        <v>166</v>
-      </c>
+      <c r="N13" s="2"/>
       <c r="O13" s="2"/>
       <c r="P13" t="s" s="2">
         <v>77</v>
@@ -2921,7 +2891,7 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
@@ -2936,21 +2906,21 @@
         <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="AL13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C14" s="2"/>
       <c r="D14" t="s" s="2">
@@ -2976,13 +2946,13 @@
         <v>101</v>
       </c>
       <c r="L14" t="s" s="2">
+        <v>168</v>
+      </c>
+      <c r="M14" t="s" s="2">
+        <v>169</v>
+      </c>
+      <c r="N14" t="s" s="2">
         <v>170</v>
-      </c>
-      <c r="M14" t="s" s="2">
-        <v>171</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>172</v>
       </c>
       <c r="O14" s="2"/>
       <c r="P14" t="s" s="2">
@@ -3032,7 +3002,7 @@
         <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3047,25 +3017,25 @@
         <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="AL14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>168</v>
+        <v>166</v>
       </c>
     </row>
     <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="E15" s="2"/>
       <c r="F15" t="s" s="2">
@@ -3084,16 +3054,16 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
+        <v>174</v>
+      </c>
+      <c r="L15" t="s" s="2">
+        <v>175</v>
+      </c>
+      <c r="M15" t="s" s="2">
         <v>176</v>
       </c>
-      <c r="L15" t="s" s="2">
+      <c r="N15" t="s" s="2">
         <v>177</v>
-      </c>
-      <c r="M15" t="s" s="2">
-        <v>178</v>
-      </c>
-      <c r="N15" t="s" s="2">
-        <v>179</v>
       </c>
       <c r="O15" s="2"/>
       <c r="P15" t="s" s="2">
@@ -3143,7 +3113,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3152,31 +3122,31 @@
         <v>79</v>
       </c>
       <c r="AI15" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AJ15" t="s" s="2">
-        <v>180</v>
+        <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="AL15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>182</v>
+        <v>77</v>
       </c>
     </row>
     <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
-        <v>184</v>
+        <v>180</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" t="s" s="2">
@@ -3195,17 +3165,15 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>185</v>
+        <v>181</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>186</v>
-      </c>
-      <c r="N16" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>182</v>
+      </c>
+      <c r="N16" s="2"/>
       <c r="O16" s="2"/>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3254,7 +3222,7 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
@@ -3263,27 +3231,27 @@
         <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AJ16" t="s" s="2">
-        <v>180</v>
+        <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="AL16" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>182</v>
+        <v>77</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3306,17 +3274,15 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>190</v>
+        <v>185</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>191</v>
+        <v>186</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>192</v>
-      </c>
-      <c r="N17" t="s" s="2">
         <v>187</v>
       </c>
+      <c r="N17" s="2"/>
       <c r="O17" s="2"/>
       <c r="P17" t="s" s="2">
         <v>77</v>
@@ -3365,7 +3331,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>189</v>
+        <v>184</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3374,10 +3340,10 @@
         <v>79</v>
       </c>
       <c r="AI17" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AJ17" t="s" s="2">
-        <v>180</v>
+        <v>99</v>
       </c>
       <c r="AK17" t="s" s="2">
         <v>77</v>
@@ -3386,15 +3352,15 @@
         <v>77</v>
       </c>
       <c r="AM17" t="s" s="2">
-        <v>182</v>
+        <v>77</v>
       </c>
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3420,13 +3386,13 @@
         <v>107</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>194</v>
+        <v>189</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>195</v>
+        <v>190</v>
       </c>
       <c r="N18" t="s" s="2">
-        <v>196</v>
+        <v>191</v>
       </c>
       <c r="O18" s="2"/>
       <c r="P18" t="s" s="2">
@@ -3452,13 +3418,13 @@
         <v>77</v>
       </c>
       <c r="X18" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="Y18" t="s" s="2">
-        <v>198</v>
+        <v>193</v>
       </c>
       <c r="Z18" t="s" s="2">
-        <v>199</v>
+        <v>194</v>
       </c>
       <c r="AA18" t="s" s="2">
         <v>77</v>
@@ -3476,7 +3442,7 @@
         <v>77</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>193</v>
+        <v>188</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>87</v>
@@ -3491,10 +3457,10 @@
         <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>201</v>
+        <v>196</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3502,14 +3468,14 @@
     </row>
     <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
-        <v>203</v>
+        <v>198</v>
       </c>
       <c r="E19" s="2"/>
       <c r="F19" t="s" s="2">
@@ -3528,16 +3494,16 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>205</v>
+        <v>200</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>206</v>
+        <v>201</v>
       </c>
       <c r="N19" t="s" s="2">
-        <v>207</v>
+        <v>202</v>
       </c>
       <c r="O19" s="2"/>
       <c r="P19" t="s" s="2">
@@ -3563,13 +3529,13 @@
         <v>77</v>
       </c>
       <c r="X19" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="Y19" t="s" s="2">
-        <v>209</v>
+        <v>204</v>
       </c>
       <c r="Z19" t="s" s="2">
-        <v>210</v>
+        <v>205</v>
       </c>
       <c r="AA19" t="s" s="2">
         <v>77</v>
@@ -3587,7 +3553,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>202</v>
+        <v>197</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3596,27 +3562,27 @@
         <v>87</v>
       </c>
       <c r="AI19" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AJ19" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>211</v>
+        <v>206</v>
       </c>
       <c r="AL19" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM19" t="s" s="2">
-        <v>212</v>
+        <v>77</v>
       </c>
     </row>
     <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3639,16 +3605,16 @@
         <v>77</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="O20" s="2"/>
       <c r="P20" t="s" s="2">
@@ -3674,13 +3640,13 @@
         <v>77</v>
       </c>
       <c r="X20" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>77</v>
@@ -3698,7 +3664,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3707,7 +3673,7 @@
         <v>79</v>
       </c>
       <c r="AI20" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
         <v>99</v>
@@ -3716,18 +3682,18 @@
         <v>77</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="AM20" t="s" s="2">
-        <v>212</v>
+        <v>77</v>
       </c>
     </row>
     <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -3753,20 +3719,20 @@
         <v>107</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>222</v>
+        <v>216</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>223</v>
+        <v>217</v>
       </c>
       <c r="O21" s="2"/>
       <c r="P21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q21" t="s" s="2">
-        <v>224</v>
+        <v>218</v>
       </c>
       <c r="R21" t="s" s="2">
         <v>77</v>
@@ -3787,13 +3753,13 @@
         <v>77</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>197</v>
+        <v>192</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>225</v>
+        <v>219</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>226</v>
+        <v>220</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>77</v>
@@ -3811,7 +3777,7 @@
         <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
@@ -3829,7 +3795,7 @@
         <v>77</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>227</v>
+        <v>221</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>77</v>
@@ -3837,10 +3803,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -3863,17 +3829,15 @@
         <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>229</v>
+        <v>223</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="N22" t="s" s="2">
-        <v>231</v>
-      </c>
+        <v>224</v>
+      </c>
+      <c r="N22" s="2"/>
       <c r="O22" s="2"/>
       <c r="P22" t="s" s="2">
         <v>77</v>
@@ -3898,13 +3862,13 @@
         <v>77</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>232</v>
+        <v>225</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>233</v>
+        <v>226</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>77</v>
@@ -3922,7 +3886,7 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>228</v>
+        <v>222</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
@@ -3931,7 +3895,7 @@
         <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AJ22" t="s" s="2">
         <v>99</v>
@@ -3943,19 +3907,19 @@
         <v>77</v>
       </c>
       <c r="AM22" t="s" s="2">
-        <v>212</v>
+        <v>77</v>
       </c>
     </row>
     <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
-        <v>235</v>
+        <v>228</v>
       </c>
       <c r="E23" s="2"/>
       <c r="F23" t="s" s="2">
@@ -3974,17 +3938,15 @@
         <v>88</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>236</v>
+        <v>229</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>237</v>
+        <v>230</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>238</v>
-      </c>
-      <c r="N23" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>231</v>
+      </c>
+      <c r="N23" s="2"/>
       <c r="O23" s="2"/>
       <c r="P23" t="s" s="2">
         <v>77</v>
@@ -4033,7 +3995,7 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>234</v>
+        <v>227</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
@@ -4042,27 +4004,27 @@
         <v>87</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>180</v>
+        <v>99</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>239</v>
+        <v>232</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>240</v>
+        <v>233</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>182</v>
+        <v>77</v>
       </c>
     </row>
     <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4085,16 +4047,16 @@
         <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>242</v>
+        <v>235</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>243</v>
+        <v>236</v>
       </c>
       <c r="N24" t="s" s="2">
-        <v>244</v>
+        <v>237</v>
       </c>
       <c r="O24" s="2"/>
       <c r="P24" t="s" s="2">
@@ -4120,13 +4082,13 @@
         <v>77</v>
       </c>
       <c r="X24" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="Y24" t="s" s="2">
-        <v>245</v>
+        <v>238</v>
       </c>
       <c r="Z24" t="s" s="2">
-        <v>246</v>
+        <v>239</v>
       </c>
       <c r="AA24" t="s" s="2">
         <v>77</v>
@@ -4144,7 +4106,7 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>241</v>
+        <v>234</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
@@ -4153,7 +4115,7 @@
         <v>87</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AJ24" t="s" s="2">
         <v>99</v>
@@ -4162,18 +4124,18 @@
         <v>77</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>212</v>
+        <v>77</v>
       </c>
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4196,16 +4158,16 @@
         <v>77</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>250</v>
+        <v>243</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>251</v>
+        <v>244</v>
       </c>
       <c r="O25" s="2"/>
       <c r="P25" t="s" s="2">
@@ -4255,7 +4217,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>248</v>
+        <v>241</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4264,27 +4226,27 @@
         <v>79</v>
       </c>
       <c r="AI25" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AJ25" t="s" s="2">
-        <v>180</v>
+        <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>182</v>
+        <v>77</v>
       </c>
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4307,16 +4269,16 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>253</v>
+        <v>246</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="O26" s="2"/>
       <c r="P26" t="s" s="2">
@@ -4366,7 +4328,7 @@
         <v>77</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>252</v>
+        <v>245</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>78</v>
@@ -4375,27 +4337,27 @@
         <v>87</v>
       </c>
       <c r="AI26" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AJ26" t="s" s="2">
-        <v>180</v>
+        <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>247</v>
+        <v>240</v>
       </c>
       <c r="AM26" t="s" s="2">
-        <v>182</v>
+        <v>77</v>
       </c>
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4418,13 +4380,13 @@
         <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" s="2"/>
@@ -4475,7 +4437,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4490,10 +4452,10 @@
         <v>99</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4501,10 +4463,10 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -4527,13 +4489,13 @@
         <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
+        <v>252</v>
+      </c>
+      <c r="L28" t="s" s="2">
+        <v>258</v>
+      </c>
+      <c r="M28" t="s" s="2">
         <v>259</v>
-      </c>
-      <c r="L28" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="M28" t="s" s="2">
-        <v>266</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -4584,7 +4546,7 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -4599,10 +4561,10 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="AM28" t="s" s="2">
         <v>77</v>
@@ -4610,10 +4572,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -4636,17 +4598,15 @@
         <v>77</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>271</v>
-      </c>
-      <c r="N29" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>264</v>
+      </c>
+      <c r="N29" s="2"/>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
         <v>77</v>
@@ -4695,7 +4655,7 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -4704,27 +4664,27 @@
         <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>180</v>
+        <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>182</v>
+        <v>77</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -4747,13 +4707,13 @@
         <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="N30" s="2"/>
       <c r="O30" s="2"/>
@@ -4804,7 +4764,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -4825,19 +4785,19 @@
         <v>77</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>279</v>
+        <v>272</v>
       </c>
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -4859,13 +4819,13 @@
         <v>132</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
@@ -4915,7 +4875,7 @@
         <v>137</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -4936,15 +4896,15 @@
         <v>77</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>279</v>
+        <v>272</v>
       </c>
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>284</v>
+        <v>277</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -4967,16 +4927,16 @@
         <v>88</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
@@ -5026,7 +4986,7 @@
         <v>77</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
@@ -5035,7 +4995,7 @@
         <v>87</v>
       </c>
       <c r="AI32" t="s" s="2">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="AJ32" t="s" s="2">
         <v>99</v>
@@ -5052,10 +5012,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>290</v>
+        <v>283</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5081,13 +5041,13 @@
         <v>101</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="O33" s="2"/>
       <c r="P33" t="s" s="2">
@@ -5113,13 +5073,13 @@
         <v>77</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>77</v>
@@ -5137,7 +5097,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5163,10 +5123,10 @@
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>298</v>
+        <v>291</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5189,16 +5149,16 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>299</v>
+        <v>292</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -5248,7 +5208,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5257,7 +5217,7 @@
         <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>99</v>
@@ -5269,15 +5229,15 @@
         <v>77</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5300,16 +5260,16 @@
         <v>88</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="O35" s="2"/>
       <c r="P35" t="s" s="2">
@@ -5359,7 +5319,7 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
@@ -5385,10 +5345,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5411,17 +5371,15 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>311</v>
+        <v>304</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>312</v>
+        <v>305</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>313</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>306</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" s="2"/>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5470,7 +5428,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>310</v>
+        <v>303</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5479,27 +5437,27 @@
         <v>87</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>180</v>
+        <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>182</v>
+        <v>77</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>314</v>
+        <v>307</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5522,13 +5480,13 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" s="2"/>
@@ -5579,7 +5537,7 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -5600,19 +5558,19 @@
         <v>77</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>279</v>
+        <v>272</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>315</v>
+        <v>308</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E38" s="2"/>
       <c r="F38" t="s" s="2">
@@ -5634,13 +5592,13 @@
         <v>132</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O38" s="2"/>
       <c r="P38" t="s" s="2">
@@ -5690,7 +5648,7 @@
         <v>137</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -5711,15 +5669,15 @@
         <v>77</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>279</v>
+        <v>272</v>
       </c>
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>316</v>
+        <v>309</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -5742,16 +5700,16 @@
         <v>88</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>285</v>
+        <v>278</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>286</v>
+        <v>279</v>
       </c>
       <c r="N39" t="s" s="2">
-        <v>287</v>
+        <v>280</v>
       </c>
       <c r="O39" s="2"/>
       <c r="P39" t="s" s="2">
@@ -5801,7 +5759,7 @@
         <v>77</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>288</v>
+        <v>281</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>78</v>
@@ -5810,7 +5768,7 @@
         <v>87</v>
       </c>
       <c r="AI39" t="s" s="2">
-        <v>289</v>
+        <v>282</v>
       </c>
       <c r="AJ39" t="s" s="2">
         <v>99</v>
@@ -5827,10 +5785,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>317</v>
+        <v>310</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -5856,13 +5814,13 @@
         <v>101</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>291</v>
+        <v>284</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>292</v>
+        <v>285</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>293</v>
+        <v>286</v>
       </c>
       <c r="O40" s="2"/>
       <c r="P40" t="s" s="2">
@@ -5888,13 +5846,13 @@
         <v>77</v>
       </c>
       <c r="X40" t="s" s="2">
-        <v>294</v>
+        <v>287</v>
       </c>
       <c r="Y40" t="s" s="2">
-        <v>295</v>
+        <v>288</v>
       </c>
       <c r="Z40" t="s" s="2">
-        <v>296</v>
+        <v>289</v>
       </c>
       <c r="AA40" t="s" s="2">
         <v>77</v>
@@ -5912,7 +5870,7 @@
         <v>77</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>297</v>
+        <v>290</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>78</v>
@@ -5938,10 +5896,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>318</v>
+        <v>311</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -5964,16 +5922,16 @@
         <v>88</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>319</v>
+        <v>312</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>300</v>
+        <v>293</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>301</v>
+        <v>294</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>302</v>
+        <v>295</v>
       </c>
       <c r="O41" s="2"/>
       <c r="P41" t="s" s="2">
@@ -6023,7 +5981,7 @@
         <v>77</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>303</v>
+        <v>296</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>78</v>
@@ -6032,7 +5990,7 @@
         <v>87</v>
       </c>
       <c r="AI41" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AJ41" t="s" s="2">
         <v>99</v>
@@ -6044,15 +6002,15 @@
         <v>77</v>
       </c>
       <c r="AM41" t="s" s="2">
-        <v>304</v>
+        <v>297</v>
       </c>
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>320</v>
+        <v>313</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6075,16 +6033,16 @@
         <v>88</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>307</v>
+        <v>300</v>
       </c>
       <c r="N42" t="s" s="2">
-        <v>308</v>
+        <v>301</v>
       </c>
       <c r="O42" s="2"/>
       <c r="P42" t="s" s="2">
@@ -6134,7 +6092,7 @@
         <v>77</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>309</v>
+        <v>302</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>78</v>
@@ -6160,10 +6118,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -6186,16 +6144,16 @@
         <v>88</v>
       </c>
       <c r="K43" t="s" s="2">
-        <v>204</v>
+        <v>199</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>322</v>
+        <v>315</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>323</v>
+        <v>316</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>324</v>
+        <v>317</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -6221,13 +6179,13 @@
         <v>77</v>
       </c>
       <c r="X43" t="s" s="2">
-        <v>208</v>
+        <v>203</v>
       </c>
       <c r="Y43" t="s" s="2">
-        <v>325</v>
+        <v>318</v>
       </c>
       <c r="Z43" t="s" s="2">
-        <v>326</v>
+        <v>319</v>
       </c>
       <c r="AA43" t="s" s="2">
         <v>77</v>
@@ -6245,7 +6203,7 @@
         <v>77</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>321</v>
+        <v>314</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>78</v>
@@ -6254,27 +6212,27 @@
         <v>79</v>
       </c>
       <c r="AI43" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AJ43" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK43" t="s" s="2">
-        <v>327</v>
+        <v>320</v>
       </c>
       <c r="AL43" t="s" s="2">
-        <v>328</v>
+        <v>321</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>329</v>
+        <v>322</v>
       </c>
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -6297,17 +6255,15 @@
         <v>88</v>
       </c>
       <c r="K44" t="s" s="2">
-        <v>331</v>
+        <v>324</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>332</v>
+        <v>325</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>333</v>
-      </c>
-      <c r="N44" t="s" s="2">
-        <v>187</v>
-      </c>
+        <v>326</v>
+      </c>
+      <c r="N44" s="2"/>
       <c r="O44" s="2"/>
       <c r="P44" t="s" s="2">
         <v>77</v>
@@ -6356,7 +6312,7 @@
         <v>77</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>330</v>
+        <v>323</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>78</v>
@@ -6365,27 +6321,27 @@
         <v>79</v>
       </c>
       <c r="AI44" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AJ44" t="s" s="2">
-        <v>180</v>
+        <v>99</v>
       </c>
       <c r="AK44" t="s" s="2">
-        <v>334</v>
+        <v>327</v>
       </c>
       <c r="AL44" t="s" s="2">
+        <v>321</v>
+      </c>
+      <c r="AM44" t="s" s="2">
         <v>328</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>335</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -6408,13 +6364,13 @@
         <v>77</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>337</v>
+        <v>330</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>339</v>
+        <v>332</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" s="2"/>
@@ -6465,7 +6421,7 @@
         <v>77</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -6474,7 +6430,7 @@
         <v>79</v>
       </c>
       <c r="AI45" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AJ45" t="s" s="2">
         <v>99</v>
@@ -6486,15 +6442,15 @@
         <v>77</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>279</v>
+        <v>77</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>340</v>
+        <v>333</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -6517,13 +6473,13 @@
         <v>77</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="N46" s="2"/>
       <c r="O46" s="2"/>
@@ -6574,7 +6530,7 @@
         <v>77</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>78</v>
@@ -6595,19 +6551,19 @@
         <v>77</v>
       </c>
       <c r="AM46" t="s" s="2">
-        <v>279</v>
+        <v>272</v>
       </c>
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>341</v>
+        <v>334</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E47" s="2"/>
       <c r="F47" t="s" s="2">
@@ -6629,13 +6585,13 @@
         <v>132</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O47" s="2"/>
       <c r="P47" t="s" s="2">
@@ -6673,19 +6629,19 @@
         <v>77</v>
       </c>
       <c r="AB47" t="s" s="2">
-        <v>135</v>
+        <v>77</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>136</v>
+        <v>77</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE47" t="s" s="2">
-        <v>137</v>
+        <v>77</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>283</v>
+        <v>276</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>78</v>
@@ -6706,19 +6662,19 @@
         <v>77</v>
       </c>
       <c r="AM47" t="s" s="2">
-        <v>279</v>
+        <v>272</v>
       </c>
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>342</v>
+        <v>335</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
-        <v>343</v>
+        <v>336</v>
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
@@ -6740,16 +6696,16 @@
         <v>132</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>344</v>
+        <v>337</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>345</v>
+        <v>338</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>77</v>
@@ -6798,7 +6754,7 @@
         <v>77</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>346</v>
+        <v>339</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -6824,10 +6780,10 @@
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -6850,13 +6806,13 @@
         <v>77</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>348</v>
+        <v>341</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>349</v>
+        <v>342</v>
       </c>
       <c r="N49" s="2"/>
       <c r="O49" s="2"/>
@@ -6907,7 +6863,7 @@
         <v>77</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>347</v>
+        <v>340</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>87</v>
@@ -6916,7 +6872,7 @@
         <v>87</v>
       </c>
       <c r="AI49" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AJ49" t="s" s="2">
         <v>99</v>
@@ -6928,15 +6884,15 @@
         <v>77</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>279</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -6959,17 +6915,15 @@
         <v>77</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>351</v>
+        <v>344</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>352</v>
+        <v>345</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="N50" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>346</v>
+      </c>
+      <c r="N50" s="2"/>
       <c r="O50" s="2"/>
       <c r="P50" t="s" s="2">
         <v>77</v>
@@ -7018,7 +6972,7 @@
         <v>77</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>350</v>
+        <v>343</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7027,19 +6981,19 @@
         <v>79</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>158</v>
+        <v>77</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK50" t="s" s="2">
-        <v>355</v>
+        <v>347</v>
       </c>
       <c r="AL50" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>356</v>
+        <v>77</v>
       </c>
     </row>
   </sheetData>
